--- a/EDRMS_Utilization_Dashboard_Checker_with_Description.xlsx
+++ b/EDRMS_Utilization_Dashboard_Checker_with_Description.xlsx
@@ -11149,7 +11149,7 @@
       </c>
       <c r="D18" s="67" t="inlineStr">
         <is>
-          <t>The first column of the site table. One row per owning unit, so units can be compared side by side.</t>
+          <t>The first column of the site table. One row per owning department, office or RM, so they can be compared side by side.</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="D19" s="82" t="inlineStr">
         <is>
-          <t>For the one unit on that row: how many EDRMS sites it owns.</t>
+          <t>For the one department, office or RM on that row: how many EDRMS sites it owns.</t>
         </is>
       </c>
       <c r="E19" s="43" t="inlineStr">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="D20" s="67" t="inlineStr">
         <is>
-          <t>For the one unit on that row: every document held across that unit's EDRMS sites.</t>
+          <t>For the one department, office or RM on that row: every document held across that row's EDRMS sites.</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="D21" s="82" t="inlineStr">
         <is>
-          <t>For the one unit on that row: how many of its documents have been declared as records.</t>
+          <t>For the one department, office or RM on that row: how many of its documents have been declared as records.</t>
         </is>
       </c>
       <c r="E21" s="43" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="D22" s="67" t="inlineStr">
         <is>
-          <t>For the one unit on that row: how many of its declared records also exist on paper.</t>
+          <t>For the one department, office or RM on that row: how many of its declared records also exist on paper.</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="D74" s="67" t="inlineStr">
         <is>
-          <t>A comparison showing, for each unit, how many documents it holds against how many it has declared.</t>
+          <t>A comparison showing, for each department, office or RM, how many documents it holds against how many it has declared.</t>
         </is>
       </c>
       <c r="E74" s="40" t="inlineStr">
@@ -21256,7 +21256,7 @@
       </c>
       <c r="D7" s="40" t="inlineStr">
         <is>
-          <t>Not a figure. The control that chooses which department, office or RM the whole screen is about.</t>
+          <t>Not a figure. The control that chooses which department, office or RM the whole screen is about. Every figure below is for that one choice only, called 'the selected department' throughout this column.</t>
         </is>
       </c>
       <c r="E7" s="40" t="inlineStr">
@@ -21287,7 +21287,7 @@
       </c>
       <c r="D8" s="43" t="inlineStr">
         <is>
-          <t>How many EDRMS sites the selected unit owns.</t>
+          <t>How many EDRMS sites the selected department owns.</t>
         </is>
       </c>
       <c r="E8" s="43" t="inlineStr">
@@ -21318,7 +21318,7 @@
       </c>
       <c r="D9" s="40" t="inlineStr">
         <is>
-          <t>How many people count as EDRMS users for the selected unit.</t>
+          <t>How many people count as EDRMS users for the selected department.</t>
         </is>
       </c>
       <c r="E9" s="40" t="inlineStr">
@@ -21349,7 +21349,7 @@
       </c>
       <c r="D10" s="43" t="inlineStr">
         <is>
-          <t>How many people visited the selected unit's EDRMS sites.</t>
+          <t>How many people visited the selected department's EDRMS sites.</t>
         </is>
       </c>
       <c r="E10" s="43" t="inlineStr">
@@ -21380,7 +21380,7 @@
       </c>
       <c r="D11" s="40" t="inlineStr">
         <is>
-          <t>Every document held across the selected unit's EDRMS sites, declared or not.</t>
+          <t>Every document held across the selected department's EDRMS sites, declared or not.</t>
         </is>
       </c>
       <c r="E11" s="40" t="inlineStr">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="D12" s="43" t="inlineStr">
         <is>
-          <t>How many of the selected unit's documents have been declared as records.</t>
+          <t>How many of the selected department's documents have been declared as records.</t>
         </is>
       </c>
       <c r="E12" s="43" t="inlineStr">
@@ -21442,7 +21442,7 @@
       </c>
       <c r="D13" s="40" t="inlineStr">
         <is>
-          <t>How many of the selected unit's declared records also exist on paper.</t>
+          <t>How many of the selected department's declared records also exist on paper.</t>
         </is>
       </c>
       <c r="E13" s="40" t="inlineStr">
@@ -21473,7 +21473,7 @@
       </c>
       <c r="D14" s="43" t="inlineStr">
         <is>
-          <t>How many of the selected unit's records reach their disposal due date.</t>
+          <t>How many of the selected department's records reach their disposal due date.</t>
         </is>
       </c>
       <c r="E14" s="43" t="inlineStr">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="D16" s="43" t="inlineStr">
         <is>
-          <t>The naming rules the selected unit's sites, libraries and folders are meant to follow.</t>
+          <t>The naming rules the selected department's sites, libraries and folders are meant to follow.</t>
         </is>
       </c>
       <c r="E16" s="43" t="inlineStr">
@@ -21562,7 +21562,7 @@
       </c>
       <c r="D17" s="40" t="inlineStr">
         <is>
-          <t>The date the selected unit started using EDRMS.</t>
+          <t>The date the selected department started using EDRMS.</t>
         </is>
       </c>
       <c r="E17" s="40" t="inlineStr">
@@ -21606,7 +21606,7 @@
       </c>
       <c r="D19" s="43" t="inlineStr">
         <is>
-          <t>How many of the selected unit's people have used EDRMS recently.</t>
+          <t>How many of the selected department's people have used EDRMS recently.</t>
         </is>
       </c>
       <c r="E19" s="43" t="inlineStr">
@@ -21637,7 +21637,7 @@
       </c>
       <c r="D20" s="40" t="inlineStr">
         <is>
-          <t>How many of the selected unit's people opened EDRMS in the last 180 days.</t>
+          <t>How many of the selected department's people opened EDRMS in the last 180 days.</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
@@ -21699,7 +21699,7 @@
       </c>
       <c r="D22" s="40" t="inlineStr">
         <is>
-          <t>How many of the selected unit's people have access to an EDRMS site but have never once opened it.</t>
+          <t>How many of the selected department's people have access to an EDRMS site but have never once opened it.</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="D23" s="43" t="inlineStr">
         <is>
-          <t>Of the selected unit's EDRMS users, how many are ADB staff.</t>
+          <t>Of the selected department's EDRMS users, how many are ADB staff.</t>
         </is>
       </c>
       <c r="E23" s="43" t="inlineStr">
@@ -21761,7 +21761,7 @@
       </c>
       <c r="D24" s="40" t="inlineStr">
         <is>
-          <t>Of the selected unit's EDRMS users, how many are contractors.</t>
+          <t>Of the selected department's EDRMS users, how many are contractors.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="D25" s="43" t="inlineStr">
         <is>
-          <t>Of the selected unit's EDRMS users, how many are consultants.</t>
+          <t>Of the selected department's EDRMS users, how many are consultants.</t>
         </is>
       </c>
       <c r="E25" s="43" t="inlineStr">
@@ -21823,7 +21823,7 @@
       </c>
       <c r="D26" s="40" t="inlineStr">
         <is>
-          <t>What share of the selected unit's EDRMS users have completed EDRMS training.</t>
+          <t>What share of the selected department's EDRMS users have completed EDRMS training.</t>
         </is>
       </c>
       <c r="E26" s="40" t="inlineStr">
@@ -21867,7 +21867,7 @@
       </c>
       <c r="D28" s="43" t="inlineStr">
         <is>
-          <t>How many EDRMS sites the selected unit owns, shown above its site table.</t>
+          <t>How many EDRMS sites the selected department owns, shown above its site table.</t>
         </is>
       </c>
       <c r="E28" s="43" t="inlineStr">
@@ -21898,7 +21898,7 @@
       </c>
       <c r="D29" s="40" t="inlineStr">
         <is>
-          <t>Every document across the selected unit's sites, shown above its site table.</t>
+          <t>Every document across the selected department's sites, shown above its site table.</t>
         </is>
       </c>
       <c r="E29" s="40" t="inlineStr">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="D30" s="43" t="inlineStr">
         <is>
-          <t>Records declared across the selected unit's sites.</t>
+          <t>Records declared across the selected department's sites.</t>
         </is>
       </c>
       <c r="E30" s="43" t="inlineStr">
@@ -21960,7 +21960,7 @@
       </c>
       <c r="D31" s="40" t="inlineStr">
         <is>
-          <t>Paper counterparts across the selected unit's sites.</t>
+          <t>Paper counterparts across the selected department's sites.</t>
         </is>
       </c>
       <c r="E31" s="40" t="inlineStr">
@@ -21991,7 +21991,7 @@
       </c>
       <c r="D32" s="43" t="inlineStr">
         <is>
-          <t>Records in the selected unit falling due for disposal within the next 12 months.</t>
+          <t>Records in the selected department falling due for disposal within the next 12 months.</t>
         </is>
       </c>
       <c r="E32" s="43" t="inlineStr">
@@ -22022,7 +22022,7 @@
       </c>
       <c r="D33" s="40" t="inlineStr">
         <is>
-          <t>One row per site. The name of each EDRMS site the selected unit owns.</t>
+          <t>One row per site. The name of each EDRMS site the selected department owns.</t>
         </is>
       </c>
       <c r="E33" s="40" t="inlineStr">
@@ -22221,7 +22221,7 @@
       </c>
       <c r="D40" s="40" t="inlineStr">
         <is>
-          <t>How many people visited the selected unit's EDRMS sites.</t>
+          <t>How many people visited the selected department's EDRMS sites.</t>
         </is>
       </c>
       <c r="E40" s="40" t="inlineStr">
@@ -22252,7 +22252,7 @@
       </c>
       <c r="D41" s="43" t="inlineStr">
         <is>
-          <t>A table showing visit activity for each of the selected unit's sites.</t>
+          <t>A table showing visit activity for each of the selected department's sites.</t>
         </is>
       </c>
       <c r="E41" s="43" t="inlineStr">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="D42" s="40" t="inlineStr">
         <is>
-          <t>How many pages were viewed in total across the selected unit's sites.</t>
+          <t>How many pages were viewed in total across the selected department's sites.</t>
         </is>
       </c>
       <c r="E42" s="40" t="inlineStr">
@@ -22523,7 +22523,7 @@
       </c>
       <c r="D50" s="40" t="inlineStr">
         <is>
-          <t>Of the people who visited the selected unit's sites, how many came from outside ADB.</t>
+          <t>Of the people who visited the selected department's sites, how many came from outside ADB.</t>
         </is>
       </c>
       <c r="E50" s="40" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="D51" s="43" t="inlineStr">
         <is>
-          <t>Of the people who visited the selected unit's sites, how many came from inside ADB.</t>
+          <t>Of the people who visited the selected department's sites, how many came from inside ADB.</t>
         </is>
       </c>
       <c r="E51" s="43" t="inlineStr">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="D52" s="40" t="inlineStr">
         <is>
-          <t>How many requests to join the selected unit's sites were approved.</t>
+          <t>How many requests to join the selected department's sites were approved.</t>
         </is>
       </c>
       <c r="E52" s="40" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="D53" s="43" t="inlineStr">
         <is>
-          <t>How many requests to join the selected unit's sites were refused.</t>
+          <t>How many requests to join the selected department's sites were refused.</t>
         </is>
       </c>
       <c r="E53" s="43" t="inlineStr">
@@ -22660,7 +22660,7 @@
       </c>
       <c r="D55" s="40" t="inlineStr">
         <is>
-          <t>How many documents have been put into the selected unit's sites.</t>
+          <t>How many documents have been put into the selected department's sites.</t>
         </is>
       </c>
       <c r="E55" s="40" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="D56" s="43" t="inlineStr">
         <is>
-          <t>How many of the selected unit's EDRMS sites are currently active.</t>
+          <t>How many of the selected department's EDRMS sites are currently active.</t>
         </is>
       </c>
       <c r="E56" s="43" t="inlineStr">
@@ -22722,7 +22722,7 @@
       </c>
       <c r="D57" s="40" t="inlineStr">
         <is>
-          <t>How much storage space the selected unit's documents occupy.</t>
+          <t>How much storage space the selected department's documents occupy.</t>
         </is>
       </c>
       <c r="E57" s="40" t="inlineStr">
@@ -22846,7 +22846,7 @@
       </c>
       <c r="D61" s="40" t="inlineStr">
         <is>
-          <t>How many distinct people created documents in the selected unit's sites.</t>
+          <t>How many distinct people created documents in the selected department's sites.</t>
         </is>
       </c>
       <c r="E61" s="40" t="inlineStr">
@@ -22890,7 +22890,7 @@
       </c>
       <c r="D63" s="43" t="inlineStr">
         <is>
-          <t>Records declared across the selected unit's sites.</t>
+          <t>Records declared across the selected department's sites.</t>
         </is>
       </c>
       <c r="E63" s="43" t="inlineStr">
@@ -22921,7 +22921,7 @@
       </c>
       <c r="D64" s="40" t="inlineStr">
         <is>
-          <t>How many distinct people in the selected unit declared at least one record.</t>
+          <t>How many distinct people in the selected department declared at least one record.</t>
         </is>
       </c>
       <c r="E64" s="40" t="inlineStr">
@@ -22952,7 +22952,7 @@
       </c>
       <c r="D65" s="43" t="inlineStr">
         <is>
-          <t>Which of the selected unit's sites have had no record declared in the last 180 days.</t>
+          <t>Which of the selected department's sites have had no record declared in the last 180 days.</t>
         </is>
       </c>
       <c r="E65" s="43" t="inlineStr">
@@ -23045,7 +23045,7 @@
       </c>
       <c r="D68" s="40" t="inlineStr">
         <is>
-          <t>How much storage space the selected unit's declared records occupy.</t>
+          <t>How much storage space the selected department's declared records occupy.</t>
         </is>
       </c>
       <c r="E68" s="40" t="inlineStr">
@@ -23151,7 +23151,7 @@
       </c>
       <c r="D72" s="43" t="inlineStr">
         <is>
-          <t>How many of the selected unit's declared records also exist on paper.</t>
+          <t>How many of the selected department's declared records also exist on paper.</t>
         </is>
       </c>
       <c r="E72" s="43" t="inlineStr">
@@ -23182,7 +23182,7 @@
       </c>
       <c r="D73" s="40" t="inlineStr">
         <is>
-          <t>The selected unit's total declared records, shown alongside for comparison.</t>
+          <t>The selected department's total declared records, shown alongside for comparison.</t>
         </is>
       </c>
       <c r="E73" s="40" t="inlineStr">
@@ -23337,7 +23337,7 @@
       </c>
       <c r="D78" s="43" t="inlineStr">
         <is>
-          <t>Of the selected unit's paper counterparts, how many have been handed over to RAC.</t>
+          <t>Of the selected department's paper counterparts, how many have been handed over to RAC.</t>
         </is>
       </c>
       <c r="E78" s="43" t="inlineStr">
@@ -23381,7 +23381,7 @@
       </c>
       <c r="D80" s="40" t="inlineStr">
         <is>
-          <t>Records in the selected unit falling due for disposal within the next 3 months.</t>
+          <t>Records in the selected department falling due for disposal within the next 3 months.</t>
         </is>
       </c>
       <c r="E80" s="40" t="inlineStr">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="D81" s="43" t="inlineStr">
         <is>
-          <t>Records in the selected unit falling due for disposal within the next 6 months.</t>
+          <t>Records in the selected department falling due for disposal within the next 6 months.</t>
         </is>
       </c>
       <c r="E81" s="43" t="inlineStr">
@@ -23443,7 +23443,7 @@
       </c>
       <c r="D82" s="40" t="inlineStr">
         <is>
-          <t>Records in the selected unit falling due for disposal within the next 12 months.</t>
+          <t>Records in the selected department falling due for disposal within the next 12 months.</t>
         </is>
       </c>
       <c r="E82" s="40" t="inlineStr">
@@ -23567,7 +23567,7 @@
       </c>
       <c r="D86" s="40" t="inlineStr">
         <is>
-          <t>Who approved each disposal in the selected unit.</t>
+          <t>Who approved each disposal in the selected department.</t>
         </is>
       </c>
       <c r="E86" s="40" t="inlineStr">
@@ -23598,7 +23598,7 @@
       </c>
       <c r="D87" s="43" t="inlineStr">
         <is>
-          <t>How many disposal requests in the selected unit were approved.</t>
+          <t>How many disposal requests in the selected department were approved.</t>
         </is>
       </c>
       <c r="E87" s="43" t="inlineStr">
@@ -23629,7 +23629,7 @@
       </c>
       <c r="D88" s="40" t="inlineStr">
         <is>
-          <t>How many disposal requests in the selected unit were declined.</t>
+          <t>How many disposal requests in the selected department were declined.</t>
         </is>
       </c>
       <c r="E88" s="40" t="inlineStr">
@@ -23691,7 +23691,7 @@
       </c>
       <c r="D90" s="40" t="inlineStr">
         <is>
-          <t>How many of the selected unit's records were actually disposed, by month and year.</t>
+          <t>How many of the selected department's records were actually disposed, by month and year.</t>
         </is>
       </c>
       <c r="E90" s="40" t="inlineStr">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="D93" s="40" t="inlineStr">
         <is>
-          <t>One row per library. The name of each library inside the selected unit's sites.</t>
+          <t>One row per library. The name of each library inside the selected department's sites.</t>
         </is>
       </c>
       <c r="E93" s="40" t="inlineStr">
@@ -23984,7 +23984,7 @@
       </c>
       <c r="D101" s="43" t="inlineStr">
         <is>
-          <t>The key dates in the EDRMS rollout programme for the selected unit.</t>
+          <t>The key dates in the EDRMS rollout programme for the selected department.</t>
         </is>
       </c>
       <c r="E101" s="43" t="n"/>
